--- a/ContenuAjoutSejour/ig/all-profiles.xlsx
+++ b/ContenuAjoutSejour/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T12:59:47+00:00</t>
+    <t>2024-10-15T15:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ContenuAjoutSejour/ig/all-profiles.xlsx
+++ b/ContenuAjoutSejour/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T15:39:02+00:00</t>
+    <t>2024-10-15T15:46:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ContenuAjoutSejour/ig/all-profiles.xlsx
+++ b/ContenuAjoutSejour/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T15:46:25+00:00</t>
+    <t>2024-10-23T12:49:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ContenuAjoutSejour/ig/all-profiles.xlsx
+++ b/ContenuAjoutSejour/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-23T12:49:02+00:00</t>
+    <t>2024-10-24T13:10:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ContenuAjoutSejour/ig/all-profiles.xlsx
+++ b/ContenuAjoutSejour/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T13:10:48+00:00</t>
+    <t>2024-10-24T14:51:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
